--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
@@ -66,13 +66,13 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>NUM-DIZ</t>
+    <t>Medizininformatik Initiative</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
+    <t>Medizininformatik Initiative (https://www.medizininformatik-initiative.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/ValueSet-mii-vs-mikrobio-empfindlichkeit-genotyp-loinc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Tests-ValueSet für die voraussichtliche Empfindlichkeit: LOINC-Codes für die aus dem Genotyp abgeleitete erwartete Wirksamkeit einer antimikrobiellen Substanz.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -359,26 +362,28 @@
       <c r="A12" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -400,7 +405,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -408,51 +413,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
